--- a/examples/08-shapes.xlsx
+++ b/examples/08-shapes.xlsx
@@ -127,6 +127,54 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:twoCellAnchor xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Frame 8"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="305496"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Behind the picture</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -152,7 +200,7 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
-  <xdr:twoCellAnchor xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
@@ -204,7 +252,7 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
@@ -252,7 +300,7 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
@@ -300,7 +348,7 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
@@ -339,7 +387,7 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
@@ -434,12 +482,110 @@
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="Link 9">
+          <a:hlinkClick r:id="rId2"/>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="DDEBF7"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="305496"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Project page</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Picture fill 10"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:blipFill>
+          <a:blip r:embed="rId3"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </a:blipFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="305496"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </wsDr>
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>

--- a/examples/08-shapes.xlsx
+++ b/examples/08-shapes.xlsx
@@ -125,8 +125,82 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Days per step</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Diagram'!$A$21:$A$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Diagram'!$B$21:$B$24</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:twoCellAnchor xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -142,7 +216,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="Frame 8"/>
+        <xdr:cNvPr id="14" name="Frame 8"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -177,6 +251,82 @@
   </xdr:twoCellAnchor>
   <oneCellAnchor>
     <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <xdr:twoCellAnchor xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="Callout 12"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="305496"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Above the chart,</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>below the picture</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <oneCellAnchor>
+    <from>
       <col>0</col>
       <colOff>0</colOff>
       <row>2</row>
@@ -185,11 +335,11 @@
     <ext cx="457200" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -215,7 +365,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="TextBox 1"/>
+        <xdr:cNvPr id="15" name="TextBox 1"/>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -267,7 +417,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Rectangle 2"/>
+        <xdr:cNvPr id="16" name="Rectangle 2"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -315,7 +465,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="Rounded Rectangle 3"/>
+        <xdr:cNvPr id="17" name="Rounded Rectangle 3"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -363,10 +513,10 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="5" name="Straight Arrow Connector 4"/>
+        <xdr:cNvPr id="18" name="Straight Arrow Connector 4"/>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="3" idx="3"/>
-          <a:endCxn id="4" idx="1"/>
+          <a:stCxn id="16" idx="3"/>
+          <a:endCxn id="17" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -402,7 +552,7 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="8" name="Group 7"/>
+        <xdr:cNvPr id="19" name="Group 7"/>
         <xdr:cNvGrpSpPr/>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
@@ -415,7 +565,7 @@
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="6" name="Oval 5"/>
+          <xdr:cNvPr id="20" name="Oval 5"/>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -448,7 +598,7 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="7" name="Oval 6"/>
+          <xdr:cNvPr id="21" name="Oval 6"/>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -497,8 +647,8 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="Link 9">
-          <a:hlinkClick r:id="rId2"/>
+        <xdr:cNvPr id="22" name="Link 9">
+          <a:hlinkClick r:id="rId3"/>
         </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
@@ -547,7 +697,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="Picture fill 10"/>
+        <xdr:cNvPr id="23" name="Picture fill 10"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -559,7 +709,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:blipFill>
-          <a:blip r:embed="rId3"/>
+          <a:blip r:embed="rId4"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -575,6 +725,61 @@
         <a:lstStyle/>
         <a:p>
           <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="Rotated 11"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="1200000">
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFD966"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="305496"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Star</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -931,7 +1136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -939,6 +1144,46 @@
         <is>
           <t>Process</t>
         </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Finish</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
